--- a/HONE_Test_Plan_AC_ACC.xlsx
+++ b/HONE_Test_Plan_AC_ACC.xlsx
@@ -697,7 +697,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Avvio di HONE: doppio click su HONE.bat (oppure launcher / 'python -m accoach ...').</t>
+          <t xml:space="preserve">  • Avvio di HONE: doppio click su HONE.bat (oppure launcher / 'python accoach_main.py ...').</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Avvia AC/ACC ed entra in una sessione di Prova. Avvia HONE (launcher o 'python -m accoach monitor').</t>
+          <t>Avvia AC/ACC ed entra in una sessione di Prova. Avvia HONE (launcher o 'python accoach_main.py monitor').</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
